--- a/data/trans_dic/P36$huevo-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,19</t>
+          <t>3,91; 8,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,85</t>
+          <t>3,51; 7,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,11</t>
+          <t>6,67; 12,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,53</t>
+          <t>1,64; 4,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,46</t>
+          <t>1,36; 4,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 12,13</t>
+          <t>6,29; 11,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,86</t>
+          <t>3,22; 5,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,39</t>
+          <t>2,85; 5,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,35</t>
+          <t>7,18; 11,3</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,2</t>
+          <t>3,22; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,2</t>
+          <t>3,9; 7,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,72</t>
+          <t>7,14; 11,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,56</t>
+          <t>1,24; 3,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,86</t>
+          <t>1,8; 4,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,43</t>
+          <t>3,73; 7,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,55</t>
+          <t>2,53; 4,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,44</t>
+          <t>3,23; 5,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,02</t>
+          <t>5,99; 8,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,75</t>
+          <t>2,46; 5,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,24</t>
+          <t>2,87; 6,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,92</t>
+          <t>5,83; 9,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,42</t>
+          <t>1,74; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,97</t>
+          <t>1,66; 3,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,83</t>
+          <t>5,77; 9,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,51</t>
+          <t>2,45; 4,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,62</t>
+          <t>2,49; 4,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,2</t>
+          <t>6,18; 9,04</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,81</t>
+          <t>2,16; 5,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,15</t>
+          <t>3,64; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,95</t>
+          <t>5,47; 9,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,27</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,67</t>
+          <t>1,65; 4,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,9</t>
+          <t>3,37; 6,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,05</t>
+          <t>1,7; 3,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,38</t>
+          <t>2,96; 5,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,78</t>
+          <t>4,79; 7,62</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,44</t>
+          <t>0,51; 3,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,45</t>
+          <t>1,95; 5,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,38</t>
+          <t>5,0; 10,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,89</t>
+          <t>0,46; 2,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,83</t>
+          <t>0,69; 3,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,11</t>
+          <t>4,09; 8,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,46</t>
+          <t>0,68; 2,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,94</t>
+          <t>1,64; 3,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,69</t>
+          <t>5,28; 8,78</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,76</t>
+          <t>0,88; 4,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,92</t>
+          <t>0,32; 2,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,32</t>
+          <t>2,61; 6,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,75</t>
+          <t>0,62; 3,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,06</t>
+          <t>0,25; 3,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,01</t>
+          <t>3,24; 8,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,21</t>
+          <t>1,08; 3,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,25</t>
+          <t>0,42; 2,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,66</t>
+          <t>3,55; 6,75</t>
         </is>
       </c>
     </row>
@@ -1343,42 +1343,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,0</t>
+          <t>0,41; 3,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,25</t>
+          <t>1,81; 6,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,72</t>
+          <t>0,33; 2,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,07</t>
+          <t>0,26; 2,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,03</t>
+          <t>2,32; 7,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,79</t>
+          <t>0,21; 1,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,52</t>
+          <t>0,62; 2,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,7</t>
+          <t>2,55; 6,11</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,34</t>
+          <t>2,95; 4,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,95</t>
+          <t>3,49; 4,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,27</t>
+          <t>6,58; 8,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,64</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,94</t>
+          <t>1,8; 2,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,89</t>
+          <t>5,39; 7,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,28</t>
+          <t>2,43; 3,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,67</t>
+          <t>2,86; 3,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,35</t>
+          <t>6,1; 7,32</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19480; 40374</t>
+          <t>19276; 41240</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16344; 35640</t>
+          <t>15960; 36109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27237; 50794</t>
+          <t>27990; 52553</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7314; 21174</t>
+          <t>7673; 22811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5876; 19102</t>
+          <t>5826; 20002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24182; 47907</t>
+          <t>24822; 46744</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30068; 56306</t>
+          <t>30895; 57034</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24207; 47558</t>
+          <t>25181; 48483</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58678; 92425</t>
+          <t>58503; 92009</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23639; 45614</t>
+          <t>23678; 46227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26486; 49428</t>
+          <t>26745; 48517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40413; 69234</t>
+          <t>42153; 70031</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7225; 22209</t>
+          <t>7759; 23031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11218; 29584</t>
+          <t>10943; 28592</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20755; 41883</t>
+          <t>21036; 42109</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34699; 61853</t>
+          <t>34446; 62148</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40631; 70428</t>
+          <t>41829; 70596</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66759; 104057</t>
+          <t>69111; 102585</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15566; 36494</t>
+          <t>15598; 36187</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19766; 42376</t>
+          <t>19490; 41486</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39372; 66355</t>
+          <t>39016; 65934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11622; 30469</t>
+          <t>12036; 30990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11519; 28129</t>
+          <t>11774; 28162</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38249; 65029</t>
+          <t>38178; 65395</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32130; 59710</t>
+          <t>32435; 61755</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35083; 64184</t>
+          <t>34580; 62717</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82243; 122382</t>
+          <t>82179; 120282</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11032; 30051</t>
+          <t>11173; 30621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21630; 43887</t>
+          <t>22337; 43577</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35886; 64085</t>
+          <t>35225; 62065</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4178; 16787</t>
+          <t>3757; 16343</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9966; 28794</t>
+          <t>10148; 30012</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21326; 44687</t>
+          <t>21806; 45079</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19111; 41718</t>
+          <t>17513; 39355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37257; 66163</t>
+          <t>36359; 65248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64086; 100534</t>
+          <t>61923; 98478</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1824; 13318</t>
+          <t>1981; 13192</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8356; 23417</t>
+          <t>8359; 25201</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24744; 49614</t>
+          <t>23873; 48009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1985; 11680</t>
+          <t>1873; 11780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4079; 17132</t>
+          <t>3062; 17443</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20075; 45278</t>
+          <t>20322; 44582</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5174; 19444</t>
+          <t>5411; 20098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14898; 34522</t>
+          <t>14388; 33016</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50800; 84697</t>
+          <t>51464; 85548</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2813; 13918</t>
+          <t>2564; 13729</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>982; 9058</t>
+          <t>980; 8430</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8694; 24464</t>
+          <t>8726; 22950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2155; 12872</t>
+          <t>2119; 12536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>894; 10818</t>
+          <t>888; 10875</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12556; 30254</t>
+          <t>12232; 30479</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6111; 20403</t>
+          <t>6871; 21496</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2905; 14910</t>
+          <t>2789; 14629</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24550; 47451</t>
+          <t>25281; 48036</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1138; 9961</t>
+          <t>1008; 9380</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4630; 15940</t>
+          <t>4617; 16208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1119; 9069</t>
+          <t>1113; 9202</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1008; 11935</t>
+          <t>1006; 11543</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8901; 28046</t>
+          <t>9267; 28322</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1119; 9715</t>
+          <t>1120; 9575</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3114; 16072</t>
+          <t>3950; 16715</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16263; 37311</t>
+          <t>16694; 39953</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>99597; 142048</t>
+          <t>96616; 143034</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>119929; 169409</t>
+          <t>119496; 167878</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>223198; 280357</t>
+          <t>223018; 285211</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55194; 89177</t>
+          <t>55733; 89664</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65029; 104497</t>
+          <t>64011; 102198</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>185120; 243954</t>
+          <t>190784; 249273</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>162591; 218052</t>
+          <t>161452; 216795</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>197467; 256117</t>
+          <t>199328; 258091</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>422647; 509481</t>
+          <t>422754; 507743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$huevo-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,36</t>
+          <t>3,96; 8,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,95</t>
+          <t>3,57; 7,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,53</t>
+          <t>6,7; 12,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,88</t>
+          <t>1,71; 4,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,67</t>
+          <t>1,4; 4,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,84</t>
+          <t>6,44; 12,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,94</t>
+          <t>3,14; 5,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,49</t>
+          <t>2,86; 5,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,3</t>
+          <t>7,18; 11,31</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,29</t>
+          <t>3,21; 6,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,07</t>
+          <t>3,87; 7,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,86</t>
+          <t>7,0; 11,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,69</t>
+          <t>1,1; 3,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,69</t>
+          <t>1,85; 4,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,47</t>
+          <t>3,74; 7,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,57</t>
+          <t>2,53; 4,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,45</t>
+          <t>3,25; 5,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,89</t>
+          <t>5,98; 8,9</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,7</t>
+          <t>2,4; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,11</t>
+          <t>2,99; 6,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,85</t>
+          <t>5,85; 10,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,49</t>
+          <t>1,81; 4,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,97</t>
+          <t>1,62; 4,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,89</t>
+          <t>5,71; 9,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,66</t>
+          <t>2,48; 4,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,52</t>
+          <t>2,56; 4,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,04</t>
+          <t>6,3; 9,34</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,92</t>
+          <t>2,28; 6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,1</t>
+          <t>3,53; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,64</t>
+          <t>5,51; 9,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,77; 3,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,87</t>
+          <t>1,61; 4,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,96</t>
+          <t>3,37; 6,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,82</t>
+          <t>1,82; 3,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,31</t>
+          <t>2,96; 5,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,62</t>
+          <t>4,81; 7,52</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,41</t>
+          <t>0,48; 3,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,87</t>
+          <t>1,95; 5,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,05</t>
+          <t>5,3; 10,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,92</t>
+          <t>0,52; 2,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,9</t>
+          <t>0,91; 3,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,97</t>
+          <t>3,93; 8,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,54</t>
+          <t>0,66; 2,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,77</t>
+          <t>1,65; 3,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,78</t>
+          <t>5,26; 8,79</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,69</t>
+          <t>0,89; 4,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,72</t>
+          <t>0,03; 2,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,86</t>
+          <t>2,6; 6,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,66</t>
+          <t>0,62; 3,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,07</t>
+          <t>0,25; 3,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,07</t>
+          <t>3,2; 7,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,38</t>
+          <t>1,06; 3,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,2</t>
+          <t>0,42; 2,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,75</t>
+          <t>3,44; 6,61</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,77</t>
+          <t>0,41; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,35</t>
+          <t>1,97; 6,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,76</t>
+          <t>0,33; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,97</t>
+          <t>0,26; 3,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,1</t>
+          <t>2,28; 6,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,76</t>
+          <t>0,21; 2,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,62</t>
+          <t>0,51; 2,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,11</t>
+          <t>2,53; 5,85</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,37</t>
+          <t>2,94; 4,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,91</t>
+          <t>3,56; 4,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,41</t>
+          <t>6,61; 8,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,66</t>
+          <t>1,64; 2,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,88</t>
+          <t>1,85; 2,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,04</t>
+          <t>5,21; 6,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,26</t>
+          <t>2,44; 3,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,7</t>
+          <t>2,83; 3,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,32</t>
+          <t>6,16; 7,39</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19276; 41240</t>
+          <t>19511; 41730</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15960; 36109</t>
+          <t>16192; 35818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27990; 52553</t>
+          <t>28092; 51211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7673; 22811</t>
+          <t>8011; 22726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5826; 20002</t>
+          <t>5986; 19935</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24822; 46744</t>
+          <t>25416; 47672</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30895; 57034</t>
+          <t>30201; 56821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25181; 48483</t>
+          <t>25229; 48935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58503; 92009</t>
+          <t>58435; 92129</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23678; 46227</t>
+          <t>23632; 46953</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26745; 48517</t>
+          <t>26573; 48998</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42153; 70031</t>
+          <t>41326; 69860</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7759; 23031</t>
+          <t>6832; 22336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10943; 28592</t>
+          <t>11287; 30010</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21036; 42109</t>
+          <t>21060; 42170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34446; 62148</t>
+          <t>34369; 62278</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41829; 70596</t>
+          <t>42104; 70869</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69111; 102585</t>
+          <t>68982; 102758</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15598; 36187</t>
+          <t>15227; 35198</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19490; 41486</t>
+          <t>20326; 42435</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39016; 65934</t>
+          <t>39174; 67239</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12036; 30990</t>
+          <t>12514; 31697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11774; 28162</t>
+          <t>11480; 28665</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38178; 65395</t>
+          <t>37746; 64478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32435; 61755</t>
+          <t>32831; 59961</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34580; 62717</t>
+          <t>35464; 61962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82179; 120282</t>
+          <t>83814; 124326</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11173; 30621</t>
+          <t>11771; 31205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22337; 43577</t>
+          <t>21668; 44686</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35225; 62065</t>
+          <t>35447; 62303</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3757; 16343</t>
+          <t>3972; 17029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10148; 30012</t>
+          <t>9942; 30427</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21806; 45079</t>
+          <t>21867; 44850</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17513; 39355</t>
+          <t>18722; 40801</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36359; 65248</t>
+          <t>36393; 66552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61923; 98478</t>
+          <t>62165; 97113</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1981; 13192</t>
+          <t>1841; 13650</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8359; 25201</t>
+          <t>8373; 23317</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23873; 48009</t>
+          <t>25332; 49256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1873; 11780</t>
+          <t>2113; 12086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3062; 17443</t>
+          <t>4045; 17132</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20322; 44582</t>
+          <t>19525; 43419</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5411; 20098</t>
+          <t>5237; 19347</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14388; 33016</t>
+          <t>14489; 33747</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51464; 85548</t>
+          <t>51225; 85673</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2564; 13729</t>
+          <t>2610; 14066</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>980; 8430</t>
+          <t>88; 8398</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8726; 22950</t>
+          <t>8698; 22889</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2119; 12536</t>
+          <t>2131; 12479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>888; 10875</t>
+          <t>895; 11442</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12232; 30479</t>
+          <t>12086; 28938</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6871; 21496</t>
+          <t>6706; 22286</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2789; 14629</t>
+          <t>2788; 14868</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25281; 48036</t>
+          <t>24508; 47067</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>0; 3341</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1008; 9380</t>
+          <t>1017; 10182</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4617; 16208</t>
+          <t>5019; 16070</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1113; 9202</t>
+          <t>1114; 9108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1006; 11543</t>
+          <t>1008; 12678</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9267; 28322</t>
+          <t>9106; 26881</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1120; 9575</t>
+          <t>1127; 11664</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3950; 16715</t>
+          <t>3256; 16532</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16694; 39953</t>
+          <t>16539; 38237</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>96616; 143034</t>
+          <t>96059; 140992</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>119496; 167878</t>
+          <t>121903; 167997</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>223018; 285211</t>
+          <t>224167; 283870</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55733; 89664</t>
+          <t>55299; 88606</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>64011; 102198</t>
+          <t>65849; 104174</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>190784; 249273</t>
+          <t>184554; 243990</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>161452; 216795</t>
+          <t>162356; 215852</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>199328; 258091</t>
+          <t>197247; 260043</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>422754; 507743</t>
+          <t>427114; 512394</t>
         </is>
       </c>
     </row>
